--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES I-X/FRACC III/LTAIPT_A63F03.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES I-X/FRACC III/LTAIPT_A63F03.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="124">
   <si>
     <t>48949</t>
   </si>
@@ -115,34 +115,154 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Dirección General</t>
+  </si>
+  <si>
+    <t>Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2010%20%20Direccion%20General.docx</t>
+  </si>
+  <si>
+    <t>Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Unidad de Control Interno</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2051%20Unidad%20de%20Control%20Interno.docx</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2047%20Direcciones%20de%20Plantel.docx</t>
+  </si>
+  <si>
+    <t>Coordinaciones Sectoriales</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2040%20Coordinaciones%20Sectoriales.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Contabilidad</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2037%20Dpto.%20de%20Contabilidad.docx</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2038%20Dpto.%20de%20Programacion%20y%20Presupuesto.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Recuros Materiales y  Servicios Generales</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2034%20Dpto.%20de%20Recursos%20Materiales%20y%20Serv.%20Grales..docx</t>
+  </si>
+  <si>
+    <t>Departamento de Recursos Humanos</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2033%20Dpto.%20de%20Recursos%20Humanos.docx</t>
+  </si>
+  <si>
+    <t>Subdirección Financiera</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2036%20Subdir.%20Financiera.docx</t>
+  </si>
+  <si>
+    <t>Departamento Inventarios</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2035%20Dpto.%20de%20Inventarios.docx</t>
+  </si>
+  <si>
+    <t>Subdirección de Servicios Adminsitrativos</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art,%2032%20Subdir.%20Servicios%20Administrativos.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Actividades Deportivas y Culturales</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2030%20Dpto.%20de%20Activ.%20Deportivas%20y%20culturales.docx</t>
+  </si>
+  <si>
+    <t>Subdirección de Actividades Paraescolares</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.29%20Subdir.%20Actividades%20Paraescolares.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Orientación Educativa y Servicio Social</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2028%20Dpto.%20de%20Orientacion%20Educ.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Control Escolar</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2027%20Dpto.%20Control%20Escolar.docx</t>
+  </si>
+  <si>
+    <t>Subdirección de Servicios Escolares</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2026%20Sub,%20Servicios%20Escolares.docx</t>
+  </si>
+  <si>
+    <t>Subdirección de Seguimiento Académico</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2021%20Subdir.%20Seguimiento%20Academico.docx</t>
+  </si>
+  <si>
+    <t>Dirección Académica</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2020%20Dir.%20Academica.docx</t>
   </si>
   <si>
     <t>Departamento de Información y Relaciones Públicas</t>
   </si>
   <si>
-    <t>Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2019%20Dpto.%20de%20Informacion%20y%20rel%20publicas.docx</t>
   </si>
   <si>
-    <t>Subdirección Jurídica</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Dirección Académica</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2020%20Dir.%20Academica.docx</t>
-  </si>
-  <si>
-    <t>Subdirección de Seguimiento Académico</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2021%20Subdir.%20Seguimiento%20Academico.docx</t>
+    <t>Departamento de Planeación e Infraestructura Institucional</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2018%20Dpto.%20de%20Planeacion.docx</t>
+  </si>
+  <si>
+    <t>Subdirección de Planeación y Evaluación Institucional</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2017%20Subdir.%20de%20Planeacion%20y%20Evaluaci%C3%B3n%20Inst..docx</t>
+  </si>
+  <si>
+    <t>Jefes de Materia</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2025%20Jefes%20de%20materia.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Bibliotecas y Laboratorios</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2024%20Dpto.%20de%20Bibliotecas%20y%20laboratorios.docx</t>
+  </si>
+  <si>
+    <t>Departamento de Formación y Desarrollo Docente</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2023%20Dpto.%20de%20formacion%20y%20desarrollo%20docente.docx</t>
   </si>
   <si>
     <t>Departamento de Planes y Programas de Estudio</t>
@@ -151,238 +271,121 @@
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2022%20Dpto.%20planes%20de%20estudio.docx</t>
   </si>
   <si>
-    <t>Departamento de  Formación y Desarrollo Docente</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2023%20Dpto.%20de%20formacion%20y%20desarrollo%20docente.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Bibliotecas y Laboratorios</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2024%20Dpto.%20de%20Bibliotecas%20y%20laboratorios.docx</t>
-  </si>
-  <si>
-    <t>Jefes de Materia</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2025%20Jefes%20de%20materia.docx</t>
-  </si>
-  <si>
-    <t>Subdirección de Servicios Escolares</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2026%20Sub,%20Servicios%20Escolares.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Control Escolar</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2027%20Dpto.%20Control%20Escolar.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Orientación Educativa y Servicio Social</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2028%20Dpto.%20de%20Orientacion%20Educ.docx</t>
-  </si>
-  <si>
-    <t>Subdirección de Actividades Paraescolares</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.29%20Subdir.%20Actividades%20Paraescolares.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Actividades Deportivas y Culturales</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2030%20Dpto.%20de%20Activ.%20Deportivas%20y%20culturales.docx</t>
-  </si>
-  <si>
-    <t>Dirección Administrativa</t>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2015%20Sub.%20Juridica.docx</t>
+  </si>
+  <si>
+    <t>Departamento Jurídico</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2016%20Dpto.%20Juridico.docx</t>
+  </si>
+  <si>
+    <t>FA97F5FD62052E4AE76F56F94A9BCCC2</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>26/06/2023</t>
+  </si>
+  <si>
+    <t>10/01/2023</t>
+  </si>
+  <si>
+    <t>8B1ED06182FA96F866E6025429BEBA46</t>
+  </si>
+  <si>
+    <t>9DEBABBAF7B2C6F76137E4244E21B6B3</t>
+  </si>
+  <si>
+    <t>3A92D028BF3E681CE23694684CC0F6AA</t>
+  </si>
+  <si>
+    <t>96C77FF41449703D5AA177703CC61AB2</t>
+  </si>
+  <si>
+    <t>Direcciones de Cada Plantel</t>
+  </si>
+  <si>
+    <t>809C19D1BCE82706CD20CFD3D0DE8FBA</t>
+  </si>
+  <si>
+    <t>F7A9BF9138D8B9EB36E2F2AEDE2257C2</t>
+  </si>
+  <si>
+    <t>Departamento de programación y Presupuesto</t>
+  </si>
+  <si>
+    <t>894D8D346E37CAE0A11CB9387487F5ED</t>
+  </si>
+  <si>
+    <t>8AA3FBEC44F6A68706CFCDC232CFD0B3</t>
+  </si>
+  <si>
+    <t>D0D06026A385EFA949233BAB39B48656</t>
+  </si>
+  <si>
+    <t>C02E40892E0349AFC87C262BA7D486C1</t>
+  </si>
+  <si>
+    <t>9E9AEEBFE03A5A71FF77F123824C91EA</t>
+  </si>
+  <si>
+    <t>6CD405AD962097FD69BA0FF7CCDF9C61</t>
+  </si>
+  <si>
+    <t>E131B0872194086219DDF8970F5EFC6F</t>
+  </si>
+  <si>
+    <t>Dirección Adminsitrativa</t>
   </si>
   <si>
     <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2031%20Direcci%C3%B3n%20Admnistrativa.docx</t>
   </si>
   <si>
-    <t>Subdirección de Servicios Administrativos</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art,%2032%20Subdir.%20Servicios%20Administrativos.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Recursos Humanos</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2033%20Dpto.%20de%20Recursos%20Humanos.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Recursos Materiales y Servicios Generales</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2034%20Dpto.%20de%20Recursos%20Materiales%20y%20Serv.%20Grales..docx</t>
-  </si>
-  <si>
-    <t>Departamento de Inventarios</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2035%20Dpto.%20de%20Inventarios.docx</t>
-  </si>
-  <si>
-    <t>Subdirección Financiera</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2036%20Subdir.%20Financiera.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Contabilidad</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2037%20Dpto.%20de%20Contabilidad.docx</t>
-  </si>
-  <si>
-    <t>Departamento de Programación y Presupuesto</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2038%20Dpto.%20de%20Programacion%20y%20Presupuesto.docx</t>
-  </si>
-  <si>
-    <t>Coordinaciones Sectoriales</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2040%20Coordinaciones%20Sectoriales.docx</t>
-  </si>
-  <si>
-    <t>Direcciones de cada Plantel</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2047%20Direcciones%20de%20Plantel.docx</t>
-  </si>
-  <si>
-    <t>Unidad de Control Interno</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2051%20Unidad%20de%20Control%20Interno.docx</t>
-  </si>
-  <si>
-    <t>Dirección General</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2010%20%20Direccion%20General.docx</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2015%20Sub.%20Juridica.docx</t>
-  </si>
-  <si>
-    <t>Departamento Jurídico</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2016%20Dpto.%20Juridico.docx</t>
-  </si>
-  <si>
-    <t>Subdirección de Planeación y Evaluación Institucional</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2017%20Subdir.%20de%20Planeacion%20y%20Evaluaci%C3%B3n%20Inst..docx</t>
-  </si>
-  <si>
-    <t>Departamento de Planeación e Infraestrucura Institucional</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Art.%2018%20Dpto.%20de%20Planeacion.docx</t>
-  </si>
-  <si>
-    <t>6AE69612B2206FE709FF5B9177A16DDF</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>10/10/2022</t>
-  </si>
-  <si>
-    <t>FC288B439259A6CC9BDB32DDA04A92C6</t>
-  </si>
-  <si>
-    <t>B56225EEF40693A55193E37E0EB61721</t>
-  </si>
-  <si>
-    <t>06E3DBEF74899E1D4592E778F3642132</t>
-  </si>
-  <si>
-    <t>2D0408F5E07FBA802E4FDADB70791405</t>
-  </si>
-  <si>
-    <t>78697E58B6361B0FDA1CC7319DB226CE</t>
-  </si>
-  <si>
-    <t>8939524FCA5C05D41583E0234EEA5249</t>
-  </si>
-  <si>
-    <t>2D36114475DFCB98F3B59E4F367F4853</t>
-  </si>
-  <si>
-    <t>D87CA9FF921DB810E81BF2515EC1DF60</t>
-  </si>
-  <si>
-    <t>D832E4F07B2B2E7F66E305083AE59B2B</t>
-  </si>
-  <si>
-    <t>C4872DA1DEA936DE2060DDF4C3CF3C09</t>
-  </si>
-  <si>
-    <t>D10810D967F9457FF7B8A4D120B8D704</t>
-  </si>
-  <si>
-    <t>DAD5E47A62E9F1FA0EB5B8BEF55B7BF6</t>
-  </si>
-  <si>
-    <t>5BDFB760FFA95540260130870A627041</t>
-  </si>
-  <si>
-    <t>F46DF60329371ABBA08BE7FEAE245203</t>
-  </si>
-  <si>
-    <t>8770F7C48C7E9A7173A91EB9B5227895</t>
-  </si>
-  <si>
-    <t>8FF0DA4D50CB75DA5DA28DD11B4E2C80</t>
-  </si>
-  <si>
-    <t>D7C05DFC8A2EC18BC0E2A78B21901093</t>
-  </si>
-  <si>
-    <t>62D6AF1D1788130A25A2DA03138BB178</t>
-  </si>
-  <si>
-    <t>E7A8B649573F5AFBB1EBB82F0C9BDA8F</t>
-  </si>
-  <si>
-    <t>A44A80420030847C15AB8A29041487A3</t>
-  </si>
-  <si>
-    <t>4823A9AE1ADBB79D61A9808B1427FC66</t>
-  </si>
-  <si>
-    <t>063D24702D034EA92FC7F7D94A191320</t>
-  </si>
-  <si>
-    <t>AB2D3C2EC23FD4D36563422518CCF68A</t>
-  </si>
-  <si>
-    <t>F2F9203E3DF0E4C63A2833AD1368C5A6</t>
-  </si>
-  <si>
-    <t>8E93C8A2D2873DF2A55B4F96AC132E46</t>
-  </si>
-  <si>
-    <t>D2B3139242EF25CCEE65D78245B2C0CC</t>
-  </si>
-  <si>
-    <t>64B8A0C9542D5D0BB2A81547D81C7A28</t>
+    <t>030C5A2A19CC8D379473C24626174E13</t>
+  </si>
+  <si>
+    <t>CB09A217E241666C0885D7602ECE2BA9</t>
+  </si>
+  <si>
+    <t>A72201270DF1A037A18CF5058AD1FC0D</t>
+  </si>
+  <si>
+    <t>C1EDF7C9F9FBE71755BAD82C29696055</t>
+  </si>
+  <si>
+    <t>3A2E1DCDA229C6BBF42596F43E848E24</t>
+  </si>
+  <si>
+    <t>68C1A5E2E956A0F08685645639637925</t>
+  </si>
+  <si>
+    <t>39313EA091879EFC669C783C6562E179</t>
+  </si>
+  <si>
+    <t>3C902B4670A97FAE6BF19B391D49DB1B</t>
+  </si>
+  <si>
+    <t>E3B0FB67F9B8E99A980C25D58B75CE61</t>
+  </si>
+  <si>
+    <t>B02E0AECE9E553F8372D77FCB4AAD3CA</t>
+  </si>
+  <si>
+    <t>FB9E3B522EBDBC5F90DD63C9FABC12CA</t>
+  </si>
+  <si>
+    <t>62A1FDFC266B3DDEFEA1DC002E539D69</t>
+  </si>
+  <si>
+    <t>786CC2571CC2F0311B44DB29A2815300</t>
+  </si>
+  <si>
+    <t>2C819B8F6C838A4BB0E3498075B8240C</t>
   </si>
 </sst>
 </file>
@@ -778,11 +781,11 @@
   <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="111.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="188" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="73.140625" bestFit="1" customWidth="1"/>
@@ -941,16 +944,16 @@
     </row>
     <row r="8" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>86</v>
@@ -965,10 +968,10 @@
         <v>37</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>38</v>
@@ -976,16 +979,16 @@
     </row>
     <row r="9" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>37</v>
@@ -1000,10 +1003,10 @@
         <v>37</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>38</v>
@@ -1011,34 +1014,34 @@
     </row>
     <row r="10" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>38</v>
@@ -1046,34 +1049,34 @@
     </row>
     <row r="11" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>38</v>
@@ -1081,34 +1084,34 @@
     </row>
     <row r="12" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>38</v>
@@ -1116,34 +1119,34 @@
     </row>
     <row r="13" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>38</v>
@@ -1151,34 +1154,34 @@
     </row>
     <row r="14" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>38</v>
@@ -1186,34 +1189,34 @@
     </row>
     <row r="15" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>38</v>
@@ -1221,34 +1224,34 @@
     </row>
     <row r="16" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>38</v>
@@ -1256,34 +1259,34 @@
     </row>
     <row r="17" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>38</v>
@@ -1291,34 +1294,34 @@
     </row>
     <row r="18" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>38</v>
@@ -1326,34 +1329,34 @@
     </row>
     <row r="19" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>38</v>
@@ -1361,34 +1364,34 @@
     </row>
     <row r="20" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>38</v>
@@ -1396,34 +1399,34 @@
     </row>
     <row r="21" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="F21" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>38</v>
@@ -1431,34 +1434,34 @@
     </row>
     <row r="22" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>38</v>
@@ -1466,34 +1469,34 @@
     </row>
     <row r="23" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>38</v>
@@ -1501,34 +1504,34 @@
     </row>
     <row r="24" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>38</v>
@@ -1536,34 +1539,34 @@
     </row>
     <row r="25" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>38</v>
@@ -1571,34 +1574,34 @@
     </row>
     <row r="26" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>38</v>
@@ -1606,34 +1609,34 @@
     </row>
     <row r="27" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>38</v>
@@ -1641,34 +1644,34 @@
     </row>
     <row r="28" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>38</v>
@@ -1676,34 +1679,34 @@
     </row>
     <row r="29" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>38</v>
@@ -1711,34 +1714,34 @@
     </row>
     <row r="30" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>38</v>
@@ -1746,34 +1749,34 @@
     </row>
     <row r="31" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>38</v>
@@ -1781,34 +1784,34 @@
     </row>
     <row r="32" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>38</v>
@@ -1816,34 +1819,34 @@
     </row>
     <row r="33" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>38</v>
@@ -1851,34 +1854,34 @@
     </row>
     <row r="34" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>38</v>
@@ -1886,34 +1889,34 @@
     </row>
     <row r="35" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>38</v>
